--- a/templates/form-10899-2500T-setup-sheet.xlsx
+++ b/templates/form-10899-2500T-setup-sheet.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -71,6 +71,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
